--- a/artfynd/A 26361-2023 artfynd.xlsx
+++ b/artfynd/A 26361-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26361-2023 artfynd.xlsx
+++ b/artfynd/A 26361-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,6 +1020,646 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115107408</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79527</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gärdsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>493864</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6937708</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115107327</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gärdsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>493688</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6937731</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115107392</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79527</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gärdsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>493806</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6937727</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115107342</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57388</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gärdsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>493699</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6937648</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115107433</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gärdsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>493845</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6937720</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115107371</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gärdsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>493806</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6937727</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26361-2023 artfynd.xlsx
+++ b/artfynd/A 26361-2023 artfynd.xlsx
@@ -2100,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117689883</v>
+        <v>117689959</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,31 +2112,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2144,10 +2148,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493679</v>
+        <v>493688</v>
       </c>
       <c r="R15" t="n">
-        <v>6937610</v>
+        <v>6937550</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,7 +2192,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2207,10 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117689959</v>
+        <v>117689883</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2219,35 +2222,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2255,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493688</v>
+        <v>493679</v>
       </c>
       <c r="R16" t="n">
-        <v>6937550</v>
+        <v>6937610</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,6 +2298,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26361-2023 artfynd.xlsx
+++ b/artfynd/A 26361-2023 artfynd.xlsx
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117689855</v>
+        <v>117689870</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,31 +1675,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1707,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493799</v>
+        <v>493792</v>
       </c>
       <c r="R11" t="n">
-        <v>6937870</v>
+        <v>6937848</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117689800</v>
+        <v>117689883</v>
       </c>
       <c r="B12" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,30 +1781,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493808</v>
+        <v>493679</v>
       </c>
       <c r="R12" t="n">
-        <v>6937872</v>
+        <v>6937610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117687279</v>
+        <v>117689800</v>
       </c>
       <c r="B13" t="n">
         <v>79561</v>
@@ -1910,19 +1910,22 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gillån (Gillån), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493795</v>
+        <v>493808</v>
       </c>
       <c r="R13" t="n">
-        <v>6937773</v>
+        <v>6937872</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1949,27 +1952,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1988,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117687442</v>
+        <v>117685812</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>91772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2000,25 +1994,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2028,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493735</v>
+        <v>493808</v>
       </c>
       <c r="R14" t="n">
-        <v>6937708</v>
+        <v>6937641</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2063,7 +2057,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2067,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117689959</v>
+        <v>117686708</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2116,45 +2110,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493688</v>
+        <v>493808</v>
       </c>
       <c r="R15" t="n">
-        <v>6937550</v>
+        <v>6937777</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2181,9 +2167,19 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,10 +2206,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117689883</v>
+        <v>117689664</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2222,42 +2218,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493679</v>
+        <v>493789</v>
       </c>
       <c r="R16" t="n">
-        <v>6937610</v>
+        <v>6937768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,22 +2300,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117686708</v>
+        <v>117687357</v>
       </c>
       <c r="B17" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2329,38 +2324,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493808</v>
+        <v>493776</v>
       </c>
       <c r="R17" t="n">
-        <v>6937777</v>
+        <v>6937744</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2392,7 +2396,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2402,7 +2406,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2535,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117689870</v>
+        <v>117689959</v>
       </c>
       <c r="B19" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,26 +2555,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2578,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493792</v>
+        <v>493688</v>
       </c>
       <c r="R19" t="n">
-        <v>6937848</v>
+        <v>6937550</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2622,7 +2631,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2641,10 +2649,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117689664</v>
+        <v>117685858</v>
       </c>
       <c r="B20" t="n">
-        <v>79561</v>
+        <v>79098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2657,40 +2665,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gärdsjön, Jmt</t>
+          <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493789</v>
+        <v>493808</v>
       </c>
       <c r="R20" t="n">
-        <v>6937768</v>
+        <v>6937643</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2717,40 +2722,49 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117685858</v>
+        <v>117687279</v>
       </c>
       <c r="B21" t="n">
-        <v>79098</v>
+        <v>79561</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,21 +2777,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2787,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493808</v>
+        <v>493795</v>
       </c>
       <c r="R21" t="n">
-        <v>6937643</v>
+        <v>6937773</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2822,7 +2836,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2832,7 +2846,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,10 +2873,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117686484</v>
+        <v>117686459</v>
       </c>
       <c r="B22" t="n">
-        <v>79562</v>
+        <v>79561</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2875,21 +2889,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2934,7 +2948,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2944,7 +2958,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2971,10 +2985,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117686459</v>
+        <v>117686417</v>
       </c>
       <c r="B23" t="n">
-        <v>79561</v>
+        <v>74584</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2987,21 +3001,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3011,10 +3025,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493865</v>
+        <v>493856</v>
       </c>
       <c r="R23" t="n">
-        <v>6937698</v>
+        <v>6937682</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3046,7 +3060,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3056,7 +3070,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3083,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117685812</v>
+        <v>117687442</v>
       </c>
       <c r="B24" t="n">
-        <v>91772</v>
+        <v>97836</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3095,25 +3109,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3123,10 +3137,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493808</v>
+        <v>493735</v>
       </c>
       <c r="R24" t="n">
-        <v>6937641</v>
+        <v>6937708</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3158,7 +3172,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3168,7 +3182,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3195,10 +3209,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117686417</v>
+        <v>117689855</v>
       </c>
       <c r="B25" t="n">
-        <v>74584</v>
+        <v>97836</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3207,41 +3221,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gillån (Gillån), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493856</v>
+        <v>493799</v>
       </c>
       <c r="R25" t="n">
-        <v>6937682</v>
+        <v>6937870</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3268,27 +3286,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3307,10 +3316,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117687357</v>
+        <v>117686484</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
+        <v>79562</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3319,47 +3328,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493776</v>
+        <v>493865</v>
       </c>
       <c r="R26" t="n">
-        <v>6937744</v>
+        <v>6937698</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 26361-2023 artfynd.xlsx
+++ b/artfynd/A 26361-2023 artfynd.xlsx
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117689870</v>
+        <v>117686708</v>
       </c>
       <c r="B11" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,22 +1697,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493792</v>
+        <v>493808</v>
       </c>
       <c r="R11" t="n">
-        <v>6937848</v>
+        <v>6937777</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1739,18 +1736,27 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117689883</v>
+        <v>117689959</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>57288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,31 +1787,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1813,10 +1823,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493679</v>
+        <v>493688</v>
       </c>
       <c r="R12" t="n">
-        <v>6937610</v>
+        <v>6937550</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,7 +1867,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1876,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117689800</v>
+        <v>117686417</v>
       </c>
       <c r="B13" t="n">
-        <v>79561</v>
+        <v>74586</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,40 +1901,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493808</v>
+        <v>493856</v>
       </c>
       <c r="R13" t="n">
-        <v>6937872</v>
+        <v>6937682</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,18 +1958,27 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1982,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117685812</v>
+        <v>117689883</v>
       </c>
       <c r="B14" t="n">
-        <v>91772</v>
+        <v>97838</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,41 +2009,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gillån (Gillån), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493808</v>
+        <v>493679</v>
       </c>
       <c r="R14" t="n">
-        <v>6937641</v>
+        <v>6937610</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2055,27 +2074,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2094,10 +2104,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117686708</v>
+        <v>117689653</v>
       </c>
       <c r="B15" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,19 +2138,22 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gillån (Gillån), Jmt</t>
+          <t>Gärdsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493808</v>
+        <v>493839</v>
       </c>
       <c r="R15" t="n">
-        <v>6937777</v>
+        <v>6937813</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2167,49 +2180,40 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117689664</v>
+        <v>117689855</v>
       </c>
       <c r="B16" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2218,41 +2222,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gärdsjön, Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493789</v>
+        <v>493799</v>
       </c>
       <c r="R16" t="n">
-        <v>6937768</v>
+        <v>6937870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,22 +2305,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117687357</v>
+        <v>117687442</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2345,26 +2350,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493776</v>
+        <v>493735</v>
       </c>
       <c r="R17" t="n">
-        <v>6937744</v>
+        <v>6937708</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2396,7 +2392,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2406,7 +2402,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,10 +2429,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117689653</v>
+        <v>117686484</v>
       </c>
       <c r="B18" t="n">
-        <v>79561</v>
+        <v>79564</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2449,40 +2445,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gärdsjön, Jmt</t>
+          <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493839</v>
+        <v>493865</v>
       </c>
       <c r="R18" t="n">
-        <v>6937813</v>
+        <v>6937698</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2509,40 +2502,49 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117689959</v>
+        <v>117687357</v>
       </c>
       <c r="B19" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,49 +2553,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493688</v>
+        <v>493776</v>
       </c>
       <c r="R19" t="n">
-        <v>6937550</v>
+        <v>6937744</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,9 +2623,19 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117685858</v>
+        <v>117689664</v>
       </c>
       <c r="B20" t="n">
-        <v>79098</v>
+        <v>79563</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2665,37 +2678,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gillån (Gillån), Jmt</t>
+          <t>Gärdsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493808</v>
+        <v>493789</v>
       </c>
       <c r="R20" t="n">
-        <v>6937643</v>
+        <v>6937768</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2722,49 +2738,40 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117687279</v>
+        <v>117685812</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>91774</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,25 +2780,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2801,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493795</v>
+        <v>493808</v>
       </c>
       <c r="R21" t="n">
-        <v>6937773</v>
+        <v>6937641</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2836,7 +2843,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2846,7 +2853,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,10 +2880,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117686459</v>
+        <v>117687279</v>
       </c>
       <c r="B22" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2913,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493865</v>
+        <v>493795</v>
       </c>
       <c r="R22" t="n">
-        <v>6937698</v>
+        <v>6937773</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2948,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2958,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,10 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117686417</v>
+        <v>117689870</v>
       </c>
       <c r="B23" t="n">
-        <v>74584</v>
+        <v>79563</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3001,37 +3008,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gillån (Gillån), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493856</v>
+        <v>493792</v>
       </c>
       <c r="R23" t="n">
-        <v>6937682</v>
+        <v>6937848</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3058,27 +3068,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3097,10 +3098,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117687442</v>
+        <v>117686459</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3109,25 +3110,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3137,10 +3138,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493735</v>
+        <v>493865</v>
       </c>
       <c r="R24" t="n">
-        <v>6937708</v>
+        <v>6937698</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3172,7 +3173,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3182,7 +3183,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3209,10 +3210,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117689855</v>
+        <v>117689800</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3221,31 +3222,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493799</v>
+        <v>493808</v>
       </c>
       <c r="R25" t="n">
-        <v>6937870</v>
+        <v>6937872</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3316,10 +3316,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117686484</v>
+        <v>117685858</v>
       </c>
       <c r="B26" t="n">
-        <v>79562</v>
+        <v>79100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493865</v>
+        <v>493808</v>
       </c>
       <c r="R26" t="n">
-        <v>6937698</v>
+        <v>6937643</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,7 +3431,7 @@
         <v>117707657</v>
       </c>
       <c r="B27" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>117734632</v>
       </c>
       <c r="B28" t="n">
-        <v>56491</v>
+        <v>56492</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 26361-2023 artfynd.xlsx
+++ b/artfynd/A 26361-2023 artfynd.xlsx
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117686708</v>
+        <v>117689959</v>
       </c>
       <c r="B11" t="n">
-        <v>79563</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,37 +1679,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gillån (Gillån), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493808</v>
+        <v>493688</v>
       </c>
       <c r="R11" t="n">
-        <v>6937777</v>
+        <v>6937550</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1736,19 +1744,9 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117689959</v>
+        <v>117686708</v>
       </c>
       <c r="B12" t="n">
-        <v>57288</v>
+        <v>79563</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,45 +1789,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493688</v>
+        <v>493808</v>
       </c>
       <c r="R12" t="n">
-        <v>6937550</v>
+        <v>6937777</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,9 +1846,19 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117686417</v>
+        <v>117689883</v>
       </c>
       <c r="B13" t="n">
-        <v>74586</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1897,41 +1897,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gillån (Gillån), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493856</v>
+        <v>493679</v>
       </c>
       <c r="R13" t="n">
-        <v>6937682</v>
+        <v>6937610</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,27 +1962,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1997,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117689883</v>
+        <v>117686417</v>
       </c>
       <c r="B14" t="n">
-        <v>97838</v>
+        <v>74586</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,45 +2004,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493679</v>
+        <v>493856</v>
       </c>
       <c r="R14" t="n">
-        <v>6937610</v>
+        <v>6937682</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,18 +2065,27 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117689653</v>
+        <v>117689855</v>
       </c>
       <c r="B15" t="n">
-        <v>79563</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2116,41 +2116,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gärdsjön, Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493839</v>
+        <v>493799</v>
       </c>
       <c r="R15" t="n">
-        <v>6937813</v>
+        <v>6937870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,22 +2199,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117689855</v>
+        <v>117689653</v>
       </c>
       <c r="B16" t="n">
-        <v>97838</v>
+        <v>79563</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2222,42 +2223,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493799</v>
+        <v>493839</v>
       </c>
       <c r="R16" t="n">
-        <v>6937870</v>
+        <v>6937813</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,12 +2305,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 26361-2023 artfynd.xlsx
+++ b/artfynd/A 26361-2023 artfynd.xlsx
@@ -2772,7 +2772,7 @@
         <v>117689959</v>
       </c>
       <c r="B21" t="n">
-        <v>57288</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 26361-2023 artfynd.xlsx
+++ b/artfynd/A 26361-2023 artfynd.xlsx
@@ -2772,7 +2772,7 @@
         <v>117689959</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 26361-2023 artfynd.xlsx
+++ b/artfynd/A 26361-2023 artfynd.xlsx
@@ -2772,7 +2772,7 @@
         <v>117689959</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 26361-2023 artfynd.xlsx
+++ b/artfynd/A 26361-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117685812</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97359439</t>
         </is>
       </c>
     </row>
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107327</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107371</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117685858</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97359440</t>
         </is>
       </c>
     </row>
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107392</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117686708</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117687279</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117689664</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117689800</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117689870</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117689959</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2118,6 +2188,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107342</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97359438</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2335,6 +2415,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117687357</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2442,6 +2527,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117687442</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2544,6 +2634,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117689855</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2646,6 +2741,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117689883</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2753,6 +2853,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117686417</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2860,6 +2965,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117686484</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2961,6 +3071,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107433</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3062,6 +3177,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115107408</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3169,6 +3289,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117686459</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3270,6 +3395,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117689653</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3375,6 +3505,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117734632</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3477,8 +3612,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117707657</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>